--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/9.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/9.xlsx
@@ -426,13 +426,13 @@
         <v>-2.852625940173073</v>
       </c>
       <c r="E2">
-        <v>-9.505216554418466</v>
+        <v>-11.95220560278094</v>
       </c>
       <c r="F2">
-        <v>-4.977143797777793</v>
+        <v>-5.065242327800326</v>
       </c>
       <c r="G2">
-        <v>-5.961685639157632</v>
+        <v>-5.150323656620627</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.447958154162899</v>
       </c>
       <c r="E3">
-        <v>-10.57678245512615</v>
+        <v>-11.6141175880946</v>
       </c>
       <c r="F3">
-        <v>-4.153899018997199</v>
+        <v>-5.277529698850561</v>
       </c>
       <c r="G3">
-        <v>-6.517481833670558</v>
+        <v>-5.131915296508688</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.107692493284841</v>
       </c>
       <c r="E4">
-        <v>-9.588509207537902</v>
+        <v>-12.53350567264925</v>
       </c>
       <c r="F4">
-        <v>-5.152392377146653</v>
+        <v>-5.303759124292804</v>
       </c>
       <c r="G4">
-        <v>-5.527852988963155</v>
+        <v>-5.216464260091891</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.726623807194158</v>
       </c>
       <c r="E5">
-        <v>-10.4368815316493</v>
+        <v>-13.19294010717155</v>
       </c>
       <c r="F5">
-        <v>-4.199914828222712</v>
+        <v>-5.122999416593118</v>
       </c>
       <c r="G5">
-        <v>-5.718471283794109</v>
+        <v>-4.957340027190124</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.287496880421497</v>
       </c>
       <c r="E6">
-        <v>-13.44344104822858</v>
+        <v>-13.29502604153583</v>
       </c>
       <c r="F6">
-        <v>-4.759810840877106</v>
+        <v>-5.045849418533387</v>
       </c>
       <c r="G6">
-        <v>-6.086296478491469</v>
+        <v>-5.307916032373999</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.756195740504822</v>
       </c>
       <c r="E7">
-        <v>-12.85055351876401</v>
+        <v>-13.46219279736018</v>
       </c>
       <c r="F7">
-        <v>-4.168134512814309</v>
+        <v>-4.77645936893857</v>
       </c>
       <c r="G7">
-        <v>-6.558334765032298</v>
+        <v>-5.536776513975581</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.114583845634818</v>
       </c>
       <c r="E8">
-        <v>-14.31013734070513</v>
+        <v>-14.82762747177876</v>
       </c>
       <c r="F8">
-        <v>-5.078169001121013</v>
+        <v>-4.798797124322462</v>
       </c>
       <c r="G8">
-        <v>-6.139352030072073</v>
+        <v>-5.434675514506322</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.352680882459754</v>
       </c>
       <c r="E9">
-        <v>-14.17929457112773</v>
+        <v>-14.87039724200185</v>
       </c>
       <c r="F9">
-        <v>-4.188601814602679</v>
+        <v>-4.924270763191906</v>
       </c>
       <c r="G9">
-        <v>-6.572430175079718</v>
+        <v>-5.230551837905539</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.469504238566236</v>
       </c>
       <c r="E10">
-        <v>-14.23450320926867</v>
+        <v>-15.85985000160635</v>
       </c>
       <c r="F10">
-        <v>-3.820550722232233</v>
+        <v>-4.637967936334133</v>
       </c>
       <c r="G10">
-        <v>-5.624497532236987</v>
+        <v>-5.13963526826461</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.467006225757425</v>
       </c>
       <c r="E11">
-        <v>-14.96394832709361</v>
+        <v>-16.16318394392653</v>
       </c>
       <c r="F11">
-        <v>-4.070743357267171</v>
+        <v>-4.579973934464139</v>
       </c>
       <c r="G11">
-        <v>-5.890412311820239</v>
+        <v>-4.932851242925482</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.36061553289962</v>
       </c>
       <c r="E12">
-        <v>-15.32294360758914</v>
+        <v>-17.31750258028142</v>
       </c>
       <c r="F12">
-        <v>-3.797447555368155</v>
+        <v>-4.279641877272553</v>
       </c>
       <c r="G12">
-        <v>-5.732062820135446</v>
+        <v>-4.539250166880061</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.161820469902927</v>
       </c>
       <c r="E13">
-        <v>-16.35014490492501</v>
+        <v>-17.85315055126721</v>
       </c>
       <c r="F13">
-        <v>-3.284087566668232</v>
+        <v>-4.553513394516514</v>
       </c>
       <c r="G13">
-        <v>-5.073596483832399</v>
+        <v>-4.250368667128784</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.894216066637362</v>
       </c>
       <c r="E14">
-        <v>-16.6714456394364</v>
+        <v>-19.08083981888653</v>
       </c>
       <c r="F14">
-        <v>-3.257461353240047</v>
+        <v>-4.070748327471588</v>
       </c>
       <c r="G14">
-        <v>-5.278918492200503</v>
+        <v>-3.886527468677464</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.577376403697897</v>
       </c>
       <c r="E15">
-        <v>-17.78602634983533</v>
+        <v>-19.11942315209418</v>
       </c>
       <c r="F15">
-        <v>-2.994146550177363</v>
+        <v>-3.956915735713685</v>
       </c>
       <c r="G15">
-        <v>-5.273981574178708</v>
+        <v>-3.699979324664055</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.230733666243806</v>
       </c>
       <c r="E16">
-        <v>-18.89160289808204</v>
+        <v>-20.55219384172221</v>
       </c>
       <c r="F16">
-        <v>-2.886286487393645</v>
+        <v>-3.649374397015535</v>
       </c>
       <c r="G16">
-        <v>-4.209560118425093</v>
+        <v>-3.255090171126213</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.872066457988728</v>
       </c>
       <c r="E17">
-        <v>-20.89853013409966</v>
+        <v>-21.27141790647674</v>
       </c>
       <c r="F17">
-        <v>-2.389627213901562</v>
+        <v>-3.367650785160437</v>
       </c>
       <c r="G17">
-        <v>-3.598909569308286</v>
+        <v>-2.951082017214027</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.506325938639708</v>
       </c>
       <c r="E18">
-        <v>-21.3323164441327</v>
+        <v>-22.25091541853563</v>
       </c>
       <c r="F18">
-        <v>-2.291076343990505</v>
+        <v>-3.277058869255478</v>
       </c>
       <c r="G18">
-        <v>-3.692773669592582</v>
+        <v>-2.536299970300903</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.14411100838883</v>
       </c>
       <c r="E19">
-        <v>-21.49183298469672</v>
+        <v>-23.69102898578595</v>
       </c>
       <c r="F19">
-        <v>-2.143404943828243</v>
+        <v>-2.681515722156413</v>
       </c>
       <c r="G19">
-        <v>-3.454911340640842</v>
+        <v>-2.270873399956189</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.785249301312686</v>
       </c>
       <c r="E20">
-        <v>-21.69213406047055</v>
+        <v>-23.25488365172041</v>
       </c>
       <c r="F20">
-        <v>-1.865456202227702</v>
+        <v>-2.499200340474269</v>
       </c>
       <c r="G20">
-        <v>-3.606861897332817</v>
+        <v>-2.042354925896043</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.431334451221033</v>
       </c>
       <c r="E21">
-        <v>-23.22810789830924</v>
+        <v>-24.94750831430898</v>
       </c>
       <c r="F21">
-        <v>-0.9714754741872531</v>
+        <v>-2.217873516605112</v>
       </c>
       <c r="G21">
-        <v>-2.996495919376442</v>
+        <v>-1.587477063552602</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.086297641488002</v>
       </c>
       <c r="E22">
-        <v>-23.04859364521618</v>
+        <v>-25.39827710544925</v>
       </c>
       <c r="F22">
-        <v>-1.512893095187399</v>
+        <v>-2.077645825924407</v>
       </c>
       <c r="G22">
-        <v>-3.258807871423959</v>
+        <v>-1.95086660318966</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.746905520095261</v>
       </c>
       <c r="E23">
-        <v>-24.70269727276696</v>
+        <v>-25.25030233915693</v>
       </c>
       <c r="F23">
-        <v>-0.8389383464741379</v>
+        <v>-1.794266307631113</v>
       </c>
       <c r="G23">
-        <v>-3.296906467242075</v>
+        <v>-2.175703927376337</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.42060805375661</v>
       </c>
       <c r="E24">
-        <v>-23.96186404948935</v>
+        <v>-25.84016633077703</v>
       </c>
       <c r="F24">
-        <v>-0.8836113721397124</v>
+        <v>-1.765488824057858</v>
       </c>
       <c r="G24">
-        <v>-2.710316540276968</v>
+        <v>-2.511521393386647</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.107989672614863</v>
       </c>
       <c r="E25">
-        <v>-25.55690070557842</v>
+        <v>-26.01454306146128</v>
       </c>
       <c r="F25">
-        <v>-0.8275698322381174</v>
+        <v>-2.090747284767084</v>
       </c>
       <c r="G25">
-        <v>-3.198363912650504</v>
+        <v>-1.704250447623917</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.812749073017396</v>
       </c>
       <c r="E26">
-        <v>-24.53844607129264</v>
+        <v>-26.23470894700177</v>
       </c>
       <c r="F26">
-        <v>-0.40645186730953</v>
+        <v>-2.309161261128424</v>
       </c>
       <c r="G26">
-        <v>-3.302506514390013</v>
+        <v>-1.981999732438686</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.542927843706706</v>
       </c>
       <c r="E27">
-        <v>-23.74300227230486</v>
+        <v>-26.43135104359842</v>
       </c>
       <c r="F27">
-        <v>-1.250173059919924</v>
+        <v>-1.99663315066542</v>
       </c>
       <c r="G27">
-        <v>-2.538874164467741</v>
+        <v>-2.096674077858746</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.301545416459756</v>
       </c>
       <c r="E28">
-        <v>-25.08072672076418</v>
+        <v>-25.97830213944083</v>
       </c>
       <c r="F28">
-        <v>-0.9254936280252554</v>
+        <v>-2.230388491326607</v>
       </c>
       <c r="G28">
-        <v>-2.508730507418747</v>
+        <v>-2.235354219794093</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.10007216265342</v>
       </c>
       <c r="E29">
-        <v>-25.05949135126033</v>
+        <v>-26.18081272363947</v>
       </c>
       <c r="F29">
-        <v>-1.372444230410145</v>
+        <v>-2.222608464679515</v>
       </c>
       <c r="G29">
-        <v>-2.610531271260028</v>
+        <v>-1.762712851252717</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.9453757013830789</v>
       </c>
       <c r="E30">
-        <v>-24.90946074536223</v>
+        <v>-26.4337059144196</v>
       </c>
       <c r="F30">
-        <v>-1.302871308983821</v>
+        <v>-2.399043266169184</v>
       </c>
       <c r="G30">
-        <v>-2.435405134832739</v>
+        <v>-1.778445198158765</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8422732337355943</v>
       </c>
       <c r="E31">
-        <v>-22.6961147532893</v>
+        <v>-25.51189235445126</v>
       </c>
       <c r="F31">
-        <v>-0.9069953555533397</v>
+        <v>-2.325272178745471</v>
       </c>
       <c r="G31">
-        <v>-2.812104250395293</v>
+        <v>-2.037968874982973</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7978197979410332</v>
       </c>
       <c r="E32">
-        <v>-24.1386828684326</v>
+        <v>-25.01542993231523</v>
       </c>
       <c r="F32">
-        <v>-1.044583867688726</v>
+        <v>-2.718822076508891</v>
       </c>
       <c r="G32">
-        <v>-3.606556440215657</v>
+        <v>-2.322764559449157</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8099032322607459</v>
       </c>
       <c r="E33">
-        <v>-22.7179274191673</v>
+        <v>-25.58967784935397</v>
       </c>
       <c r="F33">
-        <v>-0.8656300009271435</v>
+        <v>-2.719259454497569</v>
       </c>
       <c r="G33">
-        <v>-2.712402525205268</v>
+        <v>-1.719350994338916</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8779769070412513</v>
       </c>
       <c r="E34">
-        <v>-23.06270210408662</v>
+        <v>-24.78661706079645</v>
       </c>
       <c r="F34">
-        <v>-1.552945487480158</v>
+        <v>-2.486058291628855</v>
       </c>
       <c r="G34">
-        <v>-2.192707706898257</v>
+        <v>-1.553902888110885</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9975197958811617</v>
       </c>
       <c r="E35">
-        <v>-22.69047884552151</v>
+        <v>-25.06516879114137</v>
       </c>
       <c r="F35">
-        <v>-1.365820604657361</v>
+        <v>-2.49377370561853</v>
       </c>
       <c r="G35">
-        <v>-2.267863211442636</v>
+        <v>-1.761694660862183</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.158451830975111</v>
       </c>
       <c r="E36">
-        <v>-23.01319167188334</v>
+        <v>-24.54421903503415</v>
       </c>
       <c r="F36">
-        <v>-1.097388147780181</v>
+        <v>-2.150570321862458</v>
       </c>
       <c r="G36">
-        <v>-2.963736296247153</v>
+        <v>-1.687455527669285</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.355202790283606</v>
       </c>
       <c r="E37">
-        <v>-22.04573431945512</v>
+        <v>-23.3676931777254</v>
       </c>
       <c r="F37">
-        <v>-1.364449656605727</v>
+        <v>-2.595051561019603</v>
       </c>
       <c r="G37">
-        <v>-2.175732645566839</v>
+        <v>-2.121262070417851</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.575795336562449</v>
       </c>
       <c r="E38">
-        <v>-22.56794249859377</v>
+        <v>-23.23860306332708</v>
       </c>
       <c r="F38">
-        <v>-1.08202773103007</v>
+        <v>-2.165480106745446</v>
       </c>
       <c r="G38">
-        <v>-2.481059225497538</v>
+        <v>-1.567050597871732</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.810056560706927</v>
       </c>
       <c r="E39">
-        <v>-21.40667969290376</v>
+        <v>-23.16411937142761</v>
       </c>
       <c r="F39">
-        <v>-1.156887293221061</v>
+        <v>-1.908222326132032</v>
       </c>
       <c r="G39">
-        <v>-2.335502382309198</v>
+        <v>-1.943170128135058</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.049348636671021</v>
       </c>
       <c r="E40">
-        <v>-19.04704929154772</v>
+        <v>-22.79507331952599</v>
       </c>
       <c r="F40">
-        <v>-0.8423909818090062</v>
+        <v>-1.800443443353788</v>
       </c>
       <c r="G40">
-        <v>-2.885930885942795</v>
+        <v>-1.516425649505454</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.281304094301004</v>
       </c>
       <c r="E41">
-        <v>-20.18694797818281</v>
+        <v>-22.16476535602471</v>
       </c>
       <c r="F41">
-        <v>-1.005433567497616</v>
+        <v>-1.60608939820676</v>
       </c>
       <c r="G41">
-        <v>-1.990275792792515</v>
+        <v>-1.702543020661329</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.501325632492921</v>
       </c>
       <c r="E42">
-        <v>-20.65341175491961</v>
+        <v>-21.71563293014643</v>
       </c>
       <c r="F42">
-        <v>-0.3348163110502343</v>
+        <v>-1.529198679144104</v>
       </c>
       <c r="G42">
-        <v>-2.968064910779219</v>
+        <v>-1.659350862145951</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.702223114519593</v>
       </c>
       <c r="E43">
-        <v>-20.52933456659035</v>
+        <v>-21.61394985728065</v>
       </c>
       <c r="F43">
-        <v>-1.086021290278966</v>
+        <v>-1.558143492932725</v>
       </c>
       <c r="G43">
-        <v>-2.837350150591359</v>
+        <v>-1.966993172528967</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.880031636440781</v>
       </c>
       <c r="E44">
-        <v>-18.56694636882019</v>
+        <v>-20.98128286974687</v>
       </c>
       <c r="F44">
-        <v>-0.3958578765951271</v>
+        <v>-1.396378249779232</v>
       </c>
       <c r="G44">
-        <v>-2.225999921924134</v>
+        <v>-2.27863775437016</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.035827691250749</v>
       </c>
       <c r="E45">
-        <v>-18.87065825337093</v>
+        <v>-19.98044615790101</v>
       </c>
       <c r="F45">
-        <v>-0.7684161160042048</v>
+        <v>-1.266660884705246</v>
       </c>
       <c r="G45">
-        <v>-2.578473938425748</v>
+        <v>-1.919347083741149</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.167039618634484</v>
       </c>
       <c r="E46">
-        <v>-18.04212997296956</v>
+        <v>-19.41129423115784</v>
       </c>
       <c r="F46">
-        <v>-0.8097127161359685</v>
+        <v>-1.119252077009671</v>
       </c>
       <c r="G46">
-        <v>-2.044315595083969</v>
+        <v>-2.282454662962368</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.279586242546785</v>
       </c>
       <c r="E47">
-        <v>-18.32007118124973</v>
+        <v>-19.21930788445631</v>
       </c>
       <c r="F47">
-        <v>-0.8067281083836819</v>
+        <v>-0.9792637845083741</v>
       </c>
       <c r="G47">
-        <v>-3.194142338646674</v>
+        <v>-2.359283654789649</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.375456379302754</v>
       </c>
       <c r="E48">
-        <v>-16.12248247294321</v>
+        <v>-19.43915397272479</v>
       </c>
       <c r="F48">
-        <v>-1.369329568975619</v>
+        <v>-1.150137755623051</v>
       </c>
       <c r="G48">
-        <v>-2.296761543321669</v>
+        <v>-2.204364681497578</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.45733897230707</v>
       </c>
       <c r="E49">
-        <v>-16.14118438353891</v>
+        <v>-18.93666524095643</v>
       </c>
       <c r="F49">
-        <v>-1.086152172328608</v>
+        <v>-1.236659902478056</v>
       </c>
       <c r="G49">
-        <v>-2.00360625467474</v>
+        <v>-1.932659270411236</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.529956057769931</v>
       </c>
       <c r="E50">
-        <v>-15.60601403185548</v>
+        <v>-17.96397484225893</v>
       </c>
       <c r="F50">
-        <v>-1.10390657087281</v>
+        <v>-1.07360074944139</v>
       </c>
       <c r="G50">
-        <v>-1.962351268645968</v>
+        <v>-2.31885627479626</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.591077110545846</v>
       </c>
       <c r="E51">
-        <v>-15.60756317967964</v>
+        <v>-17.76834612922553</v>
       </c>
       <c r="F51">
-        <v>-0.9935738313917356</v>
+        <v>-1.119854300111506</v>
       </c>
       <c r="G51">
-        <v>-2.689649886093715</v>
+        <v>-1.999818064273034</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.64526639329059</v>
       </c>
       <c r="E52">
-        <v>-15.23676031938762</v>
+        <v>-17.161279536298</v>
       </c>
       <c r="F52">
-        <v>-0.8300160011785844</v>
+        <v>-0.8198974933533885</v>
       </c>
       <c r="G52">
-        <v>-2.804418218319056</v>
+        <v>-2.42581586994958</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.691277691290237</v>
       </c>
       <c r="E53">
-        <v>-14.89239680238946</v>
+        <v>-16.70811849543463</v>
       </c>
       <c r="F53">
-        <v>-1.154635790620252</v>
+        <v>-0.9665541434472213</v>
       </c>
       <c r="G53">
-        <v>-3.167742489341336</v>
+        <v>-2.291289422658695</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.72862994208552</v>
       </c>
       <c r="E54">
-        <v>-15.01323863909668</v>
+        <v>-16.29447941353833</v>
       </c>
       <c r="F54">
-        <v>-1.059822514430626</v>
+        <v>-0.8385142223639045</v>
       </c>
       <c r="G54">
-        <v>-2.676353363891176</v>
+        <v>-2.419362109320348</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.758887408358288</v>
       </c>
       <c r="E55">
-        <v>-13.94109128880351</v>
+        <v>-16.65459190788024</v>
       </c>
       <c r="F55">
-        <v>-0.9380831558130023</v>
+        <v>-0.9526268023039532</v>
       </c>
       <c r="G55">
-        <v>-2.659576719148682</v>
+        <v>-2.697536945503469</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.776490649899789</v>
       </c>
       <c r="E56">
-        <v>-13.52698289402751</v>
+        <v>-16.1056868863456</v>
       </c>
       <c r="F56">
-        <v>-0.8336633028531106</v>
+        <v>-0.7094512675381304</v>
       </c>
       <c r="G56">
-        <v>-2.923925051977266</v>
+        <v>-2.044352145508245</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.783149596342213</v>
       </c>
       <c r="E57">
-        <v>-13.49950940111377</v>
+        <v>-15.51461015701865</v>
       </c>
       <c r="F57">
-        <v>-0.9915426745200712</v>
+        <v>-0.7632205956538463</v>
       </c>
       <c r="G57">
-        <v>-2.202740798361906</v>
+        <v>-2.78906704012331</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.774678862798147</v>
       </c>
       <c r="E58">
-        <v>-14.3270284511632</v>
+        <v>-15.88088186375528</v>
       </c>
       <c r="F58">
-        <v>-0.9975433679859508</v>
+        <v>-0.6732590673424171</v>
       </c>
       <c r="G58">
-        <v>-2.98577359134074</v>
+        <v>-2.555285304967479</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.748560559488655</v>
       </c>
       <c r="E59">
-        <v>-12.73847495795219</v>
+        <v>-15.1112834988419</v>
       </c>
       <c r="F59">
-        <v>-0.7928231331602894</v>
+        <v>-0.5421815229930346</v>
       </c>
       <c r="G59">
-        <v>-3.732757223005482</v>
+        <v>-2.532981713925599</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.704844337965561</v>
       </c>
       <c r="E60">
-        <v>-12.30253313124156</v>
+        <v>-15.00246936213139</v>
       </c>
       <c r="F60">
-        <v>-0.804831147031271</v>
+        <v>-0.5782395276694943</v>
       </c>
       <c r="G60">
-        <v>-2.970059519646829</v>
+        <v>-2.5343915160048</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.637770032857366</v>
       </c>
       <c r="E61">
-        <v>-13.22420963523618</v>
+        <v>-15.11187325485003</v>
       </c>
       <c r="F61">
-        <v>-0.680816263158157</v>
+        <v>-0.6615003920596781</v>
       </c>
       <c r="G61">
-        <v>-3.120929228078084</v>
+        <v>-2.669051111269832</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.549596460910699</v>
       </c>
       <c r="E62">
-        <v>-11.92400114467404</v>
+        <v>-14.42290533459687</v>
       </c>
       <c r="F62">
-        <v>-0.358483596115619</v>
+        <v>-0.430869653241851</v>
       </c>
       <c r="G62">
-        <v>-3.03241715420557</v>
+        <v>-2.650052722880301</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.437464550223042</v>
       </c>
       <c r="E63">
-        <v>-12.02353285407355</v>
+        <v>-14.32405475185463</v>
       </c>
       <c r="F63">
-        <v>-0.6277336516193619</v>
+        <v>-0.2346227885794257</v>
       </c>
       <c r="G63">
-        <v>-3.35460653345027</v>
+        <v>-2.93593969858557</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.301570159623735</v>
       </c>
       <c r="E64">
-        <v>-12.22285377197472</v>
+        <v>-14.18498031743142</v>
       </c>
       <c r="F64">
-        <v>-1.006039104069063</v>
+        <v>-0.5168790406745236</v>
       </c>
       <c r="G64">
-        <v>-3.839910013258545</v>
+        <v>-3.051099642499577</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.144046571550757</v>
       </c>
       <c r="E65">
-        <v>-12.54331555779849</v>
+        <v>-14.29518993314707</v>
       </c>
       <c r="F65">
-        <v>-0.850105567431278</v>
+        <v>-0.3741132322716401</v>
       </c>
       <c r="G65">
-        <v>-3.625544385626824</v>
+        <v>-3.089775212872329</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.962960623660868</v>
       </c>
       <c r="E66">
-        <v>-10.96218800643627</v>
+        <v>-13.44880699726026</v>
       </c>
       <c r="F66">
-        <v>-0.9366070051012135</v>
+        <v>-0.5657154409065686</v>
       </c>
       <c r="G66">
-        <v>-4.416735755452888</v>
+        <v>-3.268151726315553</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.763413318194287</v>
       </c>
       <c r="E67">
-        <v>-11.16438294657422</v>
+        <v>-13.96740603575763</v>
       </c>
       <c r="F67">
-        <v>-0.9793209418591673</v>
+        <v>-0.6225290192275726</v>
       </c>
       <c r="G67">
-        <v>-3.903275395229455</v>
+        <v>-3.022062941157215</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.545328203307743</v>
       </c>
       <c r="E68">
-        <v>-12.12259525059336</v>
+        <v>-14.1322013079155</v>
       </c>
       <c r="F68">
-        <v>-0.6893302233241303</v>
+        <v>-0.47946168509007</v>
       </c>
       <c r="G68">
-        <v>-4.243711268421445</v>
+        <v>-3.372973121648752</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.312280193932197</v>
       </c>
       <c r="E69">
-        <v>-11.53283093604506</v>
+        <v>-13.98923946769225</v>
       </c>
       <c r="F69">
-        <v>-0.6199503115026578</v>
+        <v>-0.4493389328546688</v>
       </c>
       <c r="G69">
-        <v>-3.792417958401603</v>
+        <v>-3.299415392794135</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.068005056474125</v>
       </c>
       <c r="E70">
-        <v>-11.56890988282384</v>
+        <v>-13.35803856375613</v>
       </c>
       <c r="F70">
-        <v>-0.7468512274071252</v>
+        <v>-0.4396395789352894</v>
       </c>
       <c r="G70">
-        <v>-3.832033396827156</v>
+        <v>-2.689816973747547</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.812526160053854</v>
       </c>
       <c r="E71">
-        <v>-11.61993623716069</v>
+        <v>-13.52399258187363</v>
       </c>
       <c r="F71">
-        <v>-1.495277862366867</v>
+        <v>-0.4520394105877952</v>
       </c>
       <c r="G71">
-        <v>-4.119048214195786</v>
+        <v>-3.325126005527418</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.550186883002149</v>
       </c>
       <c r="E72">
-        <v>-11.16967413780205</v>
+        <v>-12.90006810417861</v>
       </c>
       <c r="F72">
-        <v>-0.8186831067408843</v>
+        <v>-0.58275661511696</v>
       </c>
       <c r="G72">
-        <v>-3.079504543650889</v>
+        <v>-2.589739301336401</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.279317174749421</v>
       </c>
       <c r="E73">
-        <v>-11.45698914404236</v>
+        <v>-13.24725995808898</v>
       </c>
       <c r="F73">
-        <v>-0.9461613947251031</v>
+        <v>-0.5525154063429584</v>
       </c>
       <c r="G73">
-        <v>-3.451196251087688</v>
+        <v>-2.858802638896536</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.001078518920649</v>
       </c>
       <c r="E74">
-        <v>-12.27395488411541</v>
+        <v>-13.27071314244029</v>
       </c>
       <c r="F74">
-        <v>-1.043352913728166</v>
+        <v>-1.012672670230681</v>
       </c>
       <c r="G74">
-        <v>-3.41011618494652</v>
+        <v>-2.845600103499277</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.7154978365524569</v>
       </c>
       <c r="E75">
-        <v>-10.40711961929558</v>
+        <v>-13.0825809758482</v>
       </c>
       <c r="F75">
-        <v>-1.09668072201819</v>
+        <v>-0.8451858934260518</v>
       </c>
       <c r="G75">
-        <v>-3.363057513691703</v>
+        <v>-2.570145663180096</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.4218238894189711</v>
       </c>
       <c r="E76">
-        <v>-11.87172052051709</v>
+        <v>-13.1227757550499</v>
       </c>
       <c r="F76">
-        <v>-1.371369837888714</v>
+        <v>-0.7409110047616499</v>
       </c>
       <c r="G76">
-        <v>-3.543606166634734</v>
+        <v>-2.684822619344747</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.1243742261329642</v>
       </c>
       <c r="E77">
-        <v>-11.55169897509376</v>
+        <v>-13.32277779960834</v>
       </c>
       <c r="F77">
-        <v>-1.403129444112047</v>
+        <v>-0.7957133070286568</v>
       </c>
       <c r="G77">
-        <v>-3.408103300866772</v>
+        <v>-2.00543638663311</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.1756829266498902</v>
       </c>
       <c r="E78">
-        <v>-12.06848306024217</v>
+        <v>-13.35400579555972</v>
       </c>
       <c r="F78">
-        <v>-2.136180751708428</v>
+        <v>-0.7812425568691523</v>
       </c>
       <c r="G78">
-        <v>-3.026352394520414</v>
+        <v>-1.87188374707471</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4724482626981015</v>
       </c>
       <c r="E79">
-        <v>-12.40770490162019</v>
+        <v>-13.87618905543042</v>
       </c>
       <c r="F79">
-        <v>-1.780403579145263</v>
+        <v>-1.256120737872025</v>
       </c>
       <c r="G79">
-        <v>-2.355866190119882</v>
+        <v>-2.159130920711949</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7614838501955117</v>
       </c>
       <c r="E80">
-        <v>-11.57749041742094</v>
+        <v>-14.4694960592388</v>
       </c>
       <c r="F80">
-        <v>-1.389696638308251</v>
+        <v>-0.950413404603673</v>
       </c>
       <c r="G80">
-        <v>-2.356380506804332</v>
+        <v>-1.995011683480795</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.038036044600069</v>
       </c>
       <c r="E81">
-        <v>-13.1124051863718</v>
+        <v>-14.32373495458262</v>
       </c>
       <c r="F81">
-        <v>-2.091950074235948</v>
+        <v>-1.310327443976419</v>
       </c>
       <c r="G81">
-        <v>-2.658088594731747</v>
+        <v>-1.449360842448936</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.29494211553094</v>
       </c>
       <c r="E82">
-        <v>-13.91614710158659</v>
+        <v>-14.92027731001304</v>
       </c>
       <c r="F82">
-        <v>-2.069479780067609</v>
+        <v>-1.567902489305106</v>
       </c>
       <c r="G82">
-        <v>-3.379883762581428</v>
+        <v>-1.560521125649357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.52786335398973</v>
       </c>
       <c r="E83">
-        <v>-14.5192266116423</v>
+        <v>-15.40893584806972</v>
       </c>
       <c r="F83">
-        <v>-1.961357953184606</v>
+        <v>-1.658740430328697</v>
       </c>
       <c r="G83">
-        <v>-1.880577526563117</v>
+        <v>-1.661267148675828</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.730251598734009</v>
       </c>
       <c r="E84">
-        <v>-15.47807020378281</v>
+        <v>-15.5873993386976</v>
       </c>
       <c r="F84">
-        <v>-1.93356539845328</v>
+        <v>-1.804733558132887</v>
       </c>
       <c r="G84">
-        <v>-2.171894851017902</v>
+        <v>-1.507494292259255</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.898199516558768</v>
       </c>
       <c r="E85">
-        <v>-15.81758276995357</v>
+        <v>-16.91585797269123</v>
       </c>
       <c r="F85">
-        <v>-2.388800503233568</v>
+        <v>-1.743108821936423</v>
       </c>
       <c r="G85">
-        <v>-2.078529402950509</v>
+        <v>-1.544739174596077</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.028076637114327</v>
       </c>
       <c r="E86">
-        <v>-17.68925652596683</v>
+        <v>-17.10372433375852</v>
       </c>
       <c r="F86">
-        <v>-2.493673473162791</v>
+        <v>-1.999398241055965</v>
       </c>
       <c r="G86">
-        <v>-2.894979726695593</v>
+        <v>-1.412176007237709</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.116139537021518</v>
       </c>
       <c r="E87">
-        <v>-18.71981361805316</v>
+        <v>-18.12801422995569</v>
       </c>
       <c r="F87">
-        <v>-2.206714579322</v>
+        <v>-2.382299475856398</v>
       </c>
       <c r="G87">
-        <v>-1.541029306532105</v>
+        <v>-1.308263151022218</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.159931398212785</v>
       </c>
       <c r="E88">
-        <v>-19.00561270215991</v>
+        <v>-19.02600912297614</v>
       </c>
       <c r="F88">
-        <v>-2.475474241323286</v>
+        <v>-2.424559467277617</v>
       </c>
       <c r="G88">
-        <v>-1.851799288935275</v>
+        <v>-1.426203537925761</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.156875999488664</v>
       </c>
       <c r="E89">
-        <v>-20.56197465439218</v>
+        <v>-20.98607567561572</v>
       </c>
       <c r="F89">
-        <v>-2.472810211755883</v>
+        <v>-2.466516276229412</v>
       </c>
       <c r="G89">
-        <v>-1.519754348859123</v>
+        <v>-1.319625111482743</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.106133785598054</v>
       </c>
       <c r="E90">
-        <v>-22.7676247458802</v>
+        <v>-22.20257203871462</v>
       </c>
       <c r="F90">
-        <v>-2.42840392039401</v>
+        <v>-3.017932291781348</v>
       </c>
       <c r="G90">
-        <v>-1.563257185980844</v>
+        <v>-0.9222045161005235</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.006799348995158</v>
       </c>
       <c r="E91">
-        <v>-23.26658324802245</v>
+        <v>-23.79365483762247</v>
       </c>
       <c r="F91">
-        <v>-2.244951190267823</v>
+        <v>-3.399168508102153</v>
       </c>
       <c r="G91">
-        <v>-1.79241007097663</v>
+        <v>-1.159134809233236</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.860695717285745</v>
       </c>
       <c r="E92">
-        <v>-25.07421033219553</v>
+        <v>-25.40683687398972</v>
       </c>
       <c r="F92">
-        <v>-3.273170512666737</v>
+        <v>-3.429419657284988</v>
       </c>
       <c r="G92">
-        <v>-1.151260803546439</v>
+        <v>-1.429628834829302</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.670989783599243</v>
       </c>
       <c r="E93">
-        <v>-27.116859338818</v>
+        <v>-26.94769488834641</v>
       </c>
       <c r="F93">
-        <v>-3.236879736750091</v>
+        <v>-3.932945268178876</v>
       </c>
       <c r="G93">
-        <v>-1.977480533551469</v>
+        <v>-1.128312358590553</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.443787553785106</v>
       </c>
       <c r="E94">
-        <v>-29.70099157833764</v>
+        <v>-29.2035573047516</v>
       </c>
       <c r="F94">
-        <v>-3.063412147297249</v>
+        <v>-4.036945138865549</v>
       </c>
       <c r="G94">
-        <v>-1.754016461019718</v>
+        <v>-1.688891437194398</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.188851121690568</v>
       </c>
       <c r="E95">
-        <v>-31.11753982453089</v>
+        <v>-31.14149970066382</v>
       </c>
       <c r="F95">
-        <v>-3.607042337630272</v>
+        <v>-4.617553650059541</v>
       </c>
       <c r="G95">
-        <v>-2.433956171584672</v>
+        <v>-1.757219844633015</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.9161008732627012</v>
       </c>
       <c r="E96">
-        <v>-34.21981424930217</v>
+        <v>-32.52379433645554</v>
       </c>
       <c r="F96">
-        <v>-4.034583463400167</v>
+        <v>-4.666141540070747</v>
       </c>
       <c r="G96">
-        <v>-2.717817209487237</v>
+        <v>-2.032152136033972</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.640012897559066</v>
       </c>
       <c r="E97">
-        <v>-36.48422397461385</v>
+        <v>-35.76762889262794</v>
       </c>
       <c r="F97">
-        <v>-3.883422979737313</v>
+        <v>-5.035687007235842</v>
       </c>
       <c r="G97">
-        <v>-2.363095341892675</v>
+        <v>-2.073101664945584</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.3749284797344963</v>
       </c>
       <c r="E98">
-        <v>-39.20969830194007</v>
+        <v>-37.57657669800231</v>
       </c>
       <c r="F98">
-        <v>-4.054478363313203</v>
+        <v>-5.522636158032309</v>
       </c>
       <c r="G98">
-        <v>-3.004667549946627</v>
+        <v>-2.567242515194778</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.1365299872499173</v>
       </c>
       <c r="E99">
-        <v>-40.20832135214979</v>
+        <v>-40.3305939701584</v>
       </c>
       <c r="F99">
-        <v>-4.755934909799407</v>
+        <v>-5.75786019409866</v>
       </c>
       <c r="G99">
-        <v>-3.626609569419998</v>
+        <v>-2.482839753308677</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.05921412979806363</v>
       </c>
       <c r="E100">
-        <v>-43.26244759803233</v>
+        <v>-42.14797487112784</v>
       </c>
       <c r="F100">
-        <v>-4.791387377904421</v>
+        <v>-5.923250373006804</v>
       </c>
       <c r="G100">
-        <v>-3.623445346975569</v>
+        <v>-2.975307116274967</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.1981326604234831</v>
       </c>
       <c r="E101">
-        <v>-44.86661508921904</v>
+        <v>-45.61540275048654</v>
       </c>
       <c r="F101">
-        <v>-4.186490306092943</v>
+        <v>-6.3396367033306</v>
       </c>
       <c r="G101">
-        <v>-3.206981980545769</v>
+        <v>-3.366401877512919</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.2696748519170241</v>
       </c>
       <c r="E102">
-        <v>-47.70120050786549</v>
+        <v>-47.29763192512906</v>
       </c>
       <c r="F102">
-        <v>-5.450812562372578</v>
+        <v>-6.803809064019692</v>
       </c>
       <c r="G102">
-        <v>-4.101665876708154</v>
+        <v>-3.474392716779729</v>
       </c>
     </row>
   </sheetData>
